--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>patient-initiated</t>
+  </si>
+  <si>
+    <t>Patient initiated</t>
   </si>
   <si>
     <t>Patient no longer wants to participate in the ACCESS Model after the initial 90-day lock-in period.</t>
@@ -555,7 +558,9 @@
       <c r="C5" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/CodeSystem/ACCESSUnalignmentReasonCS</t>
+    <t>https://dsacms.github.io/cmmi-access-model/CodeSystem/ACCESSUnalignmentReasonCS</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
+++ b/CodeSystem-ACCESSUnalignmentReasonCS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
